--- a/clases/data/II-1123_04_Datos y ejercicios resueltos.xlsx
+++ b/clases/data/II-1123_04_Datos y ejercicios resueltos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve\Dropbox\Sitio personal\stevenggoni.github.io\clases\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1255C883-39B5-440F-ACD0-7C66DFC950E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D225C60D-37BC-4DF2-B532-991404380E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="3" activeTab="5" xr2:uid="{212DB067-01D2-461B-B590-358867CFA2E8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{212DB067-01D2-461B-B590-358867CFA2E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos - Ejemplo 01" sheetId="2" r:id="rId1"/>
@@ -811,6 +811,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -818,7 +819,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1216,6 +1216,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1223,7 +1224,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2835,14 +2835,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB7E0950-77B7-42A7-8828-573A92916B8B}">
   <dimension ref="B2:D22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B3" s="2">
         <v>1</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>23.75</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>11</v>
       </c>
@@ -2974,7 +2974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B14" s="2">
         <v>12</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B15" s="2">
         <v>13</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B16" s="2">
         <v>14</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="2">
         <v>15</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="2">
         <v>16</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="2">
         <v>17</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="2">
         <v>18</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="2">
         <v>19</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="2">
         <v>20</v>
       </c>
@@ -3081,33 +3081,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E9FDC3C-6F10-4D52-8135-C7D77A952D36}">
   <dimension ref="B2:W26"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.88671875" style="1"/>
-    <col min="15" max="15" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.88671875" style="1"/>
-    <col min="18" max="18" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.90625" style="1"/>
+    <col min="10" max="10" width="7.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.90625" style="1"/>
+    <col min="15" max="15" width="11.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.90625" style="1"/>
+    <col min="18" max="18" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="8.88671875" style="1"/>
+    <col min="23" max="23" width="7.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="2">
         <v>1</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>166254.85806698122</v>
       </c>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>1693737.6013749987</v>
       </c>
     </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>9236.3810037211788</v>
       </c>
     </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>65.088687062092959</v>
       </c>
     </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>44.183911798178634</v>
       </c>
     </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>2.889106548921919</v>
       </c>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>48.56382367642982</v>
       </c>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -3467,7 +3467,7 @@
       <c r="V10" s="31"/>
       <c r="W10" s="31"/>
     </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>11</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>8.2167161963297985E-11</v>
       </c>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>12</v>
       </c>
@@ -3663,7 +3663,7 @@
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>13</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>80.817414621334819</v>
       </c>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>14</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>15</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>2720.6493131221564</v>
       </c>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>16</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>-31.083803319670487</v>
       </c>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>17</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>9.4991866681348256</v>
       </c>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>18</v>
       </c>
@@ -3888,7 +3888,7 @@
       <c r="V20" s="31"/>
       <c r="W20" s="31"/>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>19</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>20</v>
       </c>
@@ -3986,11 +3986,11 @@
         <v>165.37675770333172</v>
       </c>
       <c r="W22" s="3">
-        <f>1-_xlfn.F.DIST(V22,S22,S24,TRUE)</f>
-        <v>7.9812378928068028E-11</v>
-      </c>
-    </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
+        <f>1-_xlfn.F.DIST(V22,S22,S23,TRUE)</f>
+        <v>1.6433432392659597E-10</v>
+      </c>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.3">
       <c r="O23" s="5" t="s">
         <v>14</v>
       </c>
@@ -4015,7 +4015,7 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:23" x14ac:dyDescent="0.3">
       <c r="R24" s="5" t="s">
         <v>37</v>
       </c>
@@ -4034,7 +4034,7 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:23" x14ac:dyDescent="0.3">
       <c r="R26" s="5" t="s">
         <v>38</v>
       </c>
@@ -4057,24 +4057,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE2F5409-95ED-4A7B-96BD-00F632011131}">
   <dimension ref="B2:AD45"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.90625" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.88671875" customWidth="1"/>
-    <col min="10" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.90625" customWidth="1"/>
+    <col min="10" max="10" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" customWidth="1"/>
+    <col min="12" max="12" width="9.08984375" customWidth="1"/>
     <col min="13" max="23" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B3" s="2">
         <v>1</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>267.25</v>
       </c>
     </row>
-    <row r="4" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>4677.6875</v>
       </c>
     </row>
-    <row r="5" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -4182,7 +4182,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -4222,7 +4222,7 @@
       <c r="V7" s="23"/>
       <c r="W7" s="23"/>
     </row>
-    <row r="8" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>9.037020720194073E-4</v>
       </c>
     </row>
-    <row r="9" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>-4.8266162852761502E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>7.3538756110579258E-3</v>
       </c>
     </row>
-    <row r="12" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>11</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B14" s="2">
         <v>12</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B15" s="2">
         <v>13</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B16" s="2">
         <v>14</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B17" s="2">
         <v>15</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>96.106092438102863</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B18" s="2">
         <v>16</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>-67.274574059797033</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B19" s="2">
         <v>17</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>-14.593631442055539</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B20" s="2">
         <v>18</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>-111.53594099930176</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B21" s="2">
         <v>19</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>8.3469366510235172</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B22" s="2">
         <v>20</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>-213.60413104809732</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.35">
       <c r="K23" s="19">
         <v>48.563823676429138</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
       <c r="K24" s="19">
         <v>40.061618360964985</v>
       </c>
@@ -4717,102 +4717,102 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
       <c r="K25" s="19">
         <v>8.7295730854916656</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="H26" s="25"/>
       <c r="K26" s="19">
         <v>37.567141392660233</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
       <c r="H27" s="25"/>
       <c r="K27" s="19">
         <v>20.374323282470868</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
       <c r="H28" s="25"/>
       <c r="K28" s="19">
         <v>-88.946392957902845</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
       <c r="H29" s="25"/>
       <c r="K29" s="19">
         <v>80.817414621334365</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.35">
       <c r="H30" s="25"/>
       <c r="K30" s="19">
         <v>71.175152711528426</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
       <c r="H31" s="25"/>
       <c r="K31" s="19">
         <v>-45.143358213381589</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.35">
       <c r="H32" s="25"/>
       <c r="K32" s="19">
         <v>94.442278006997412</v>
       </c>
     </row>
-    <row r="33" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H33" s="25"/>
       <c r="K33" s="19">
         <v>9.4991866681339161</v>
       </c>
     </row>
-    <row r="34" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H34" s="25"/>
       <c r="K34" s="19">
         <v>37.097527810018164</v>
       </c>
     </row>
-    <row r="35" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H35" s="25"/>
       <c r="K35" s="19">
         <v>100.68482288851237</v>
       </c>
     </row>
-    <row r="36" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H36" s="25"/>
       <c r="K36" s="19">
         <v>-75.32015368583393</v>
       </c>
     </row>
-    <row r="37" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H37" s="25"/>
     </row>
-    <row r="38" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H38" s="25"/>
     </row>
-    <row r="39" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H39" s="25"/>
     </row>
-    <row r="40" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H40" s="25"/>
     </row>
-    <row r="41" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H41" s="25"/>
     </row>
-    <row r="42" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H42" s="25"/>
     </row>
-    <row r="43" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H43" s="25"/>
     </row>
-    <row r="44" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H44" s="25"/>
     </row>
-    <row r="45" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H45" s="25"/>
     </row>
   </sheetData>
@@ -4823,15 +4823,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5441A05E-7673-4E59-8908-8A881A0E35FC}">
   <dimension ref="B2:C16"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.90625" style="1"/>
+    <col min="2" max="2" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>65</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>41</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>41</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>41</v>
       </c>
@@ -4879,7 +4879,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>41</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>41</v>
       </c>
@@ -4895,7 +4895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>42</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>42</v>
       </c>
@@ -4959,37 +4959,37 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB288EC2-D9B9-4C30-9ECF-ACFA827222F8}">
   <dimension ref="B2:AD26"/>
-  <sheetFormatPr defaultColWidth="15.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="15.08984375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" style="12" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.36328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="3" style="12" customWidth="1"/>
-    <col min="8" max="8" width="7.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="5" style="12" customWidth="1"/>
-    <col min="13" max="13" width="10.109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.21875" style="12" customWidth="1"/>
-    <col min="15" max="15" width="9.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.88671875" style="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.88671875" style="12" customWidth="1"/>
-    <col min="19" max="19" width="7.88671875" style="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.21875" style="12" customWidth="1"/>
-    <col min="21" max="21" width="3.5546875" style="12" customWidth="1"/>
-    <col min="22" max="22" width="11.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.21875" style="12" customWidth="1"/>
-    <col min="25" max="25" width="10.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="7.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="7.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="15.109375" style="12"/>
+    <col min="13" max="13" width="10.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.1796875" style="12" customWidth="1"/>
+    <col min="15" max="15" width="9.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.36328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.90625" style="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.90625" style="12" customWidth="1"/>
+    <col min="19" max="19" width="7.90625" style="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.1796875" style="12" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" style="12" customWidth="1"/>
+    <col min="22" max="22" width="11.453125" style="12" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.1796875" style="12" customWidth="1"/>
+    <col min="25" max="25" width="10.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.81640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.36328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="7.81640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7.453125" style="12" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="15.08984375" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B2" s="14" t="s">
         <v>40</v>
       </c>
@@ -5045,7 +5045,7 @@
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
     </row>
-    <row r="3" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B3" s="14" t="s">
         <v>41</v>
       </c>
@@ -5114,7 +5114,7 @@
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
     </row>
-    <row r="4" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B4" s="14" t="s">
         <v>41</v>
       </c>
@@ -5183,7 +5183,7 @@
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B5" s="14" t="s">
         <v>41</v>
       </c>
@@ -5252,7 +5252,7 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B6" s="14" t="s">
         <v>41</v>
       </c>
@@ -5311,7 +5311,7 @@
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
     </row>
-    <row r="7" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B7" s="14" t="s">
         <v>41</v>
       </c>
@@ -5372,15 +5372,15 @@
         <v>20</v>
       </c>
       <c r="Z7" s="7">
-        <f>+SQRT(Z5*((1/20)+(POWER(T3,2)/T4)))</f>
-        <v>0.4094961230951179</v>
+        <f>+SQRT(Z5*((1/14)+(POWER(T3,2)/T4)))</f>
+        <v>0.44416090728994351</v>
       </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
     </row>
-    <row r="8" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B8" s="14" t="s">
         <v>41</v>
       </c>
@@ -5449,7 +5449,7 @@
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
     </row>
-    <row r="9" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B9" s="14" t="s">
         <v>41</v>
       </c>
@@ -5506,7 +5506,7 @@
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
     </row>
-    <row r="10" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B10" s="14" t="s">
         <v>42</v>
       </c>
@@ -5565,7 +5565,7 @@
       <c r="AC10" s="31"/>
       <c r="AD10" s="31"/>
     </row>
-    <row r="11" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B11" s="14" t="s">
         <v>42</v>
       </c>
@@ -5634,7 +5634,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B12" s="14" t="s">
         <v>42</v>
       </c>
@@ -5696,18 +5696,18 @@
       </c>
       <c r="AB12" s="3">
         <f>+Z7</f>
-        <v>0.4094961230951179</v>
+        <v>0.44416090728994351</v>
       </c>
       <c r="AC12" s="3">
         <f>+(AA12-0)/AB12</f>
-        <v>19.885065287823778</v>
+        <v>18.333124345726294</v>
       </c>
       <c r="AD12" s="6">
         <f>1-_xlfn.T.DIST(ABS(AC12),Z14,TRUE)</f>
-        <v>7.4592776400095318E-11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:30" x14ac:dyDescent="0.3">
+        <v>1.9214785318411032E-10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B13" s="14" t="s">
         <v>42</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>4.9703963655234329E-4</v>
       </c>
     </row>
-    <row r="14" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B14" s="14" t="s">
         <v>42</v>
       </c>
@@ -5841,7 +5841,7 @@
       <c r="AC14" s="2"/>
       <c r="AD14" s="2"/>
     </row>
-    <row r="15" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B15" s="14" t="s">
         <v>42</v>
       </c>
@@ -5898,7 +5898,7 @@
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
     </row>
-    <row r="16" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B16" s="14" t="s">
         <v>42</v>
       </c>
@@ -5961,7 +5961,7 @@
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
     </row>
-    <row r="17" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:30" x14ac:dyDescent="0.35">
       <c r="B17" s="15"/>
       <c r="V17" s="5" t="s">
         <v>14</v>
@@ -5976,17 +5976,17 @@
       </c>
       <c r="Z17" s="3">
         <f>+AA12-AB12*_xlfn.T.INV.2T(0.05,18)</f>
-        <v>7.2825377124533519</v>
+        <v>7.2097097033182438</v>
       </c>
       <c r="AA17" s="3">
         <f>+AA12+AB12*_xlfn.T.INV.2T(0.05,18)</f>
-        <v>9.0031765732609319</v>
+        <v>9.0760045823960418</v>
       </c>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
     </row>
-    <row r="18" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:30" x14ac:dyDescent="0.35">
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
@@ -6005,7 +6005,7 @@
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
     </row>
-    <row r="19" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:30" x14ac:dyDescent="0.35">
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
@@ -6016,7 +6016,7 @@
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
     </row>
-    <row r="20" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:30" x14ac:dyDescent="0.35">
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
@@ -6029,7 +6029,7 @@
       <c r="AC20" s="31"/>
       <c r="AD20" s="31"/>
     </row>
-    <row r="21" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:30" x14ac:dyDescent="0.35">
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
@@ -6052,7 +6052,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:30" x14ac:dyDescent="0.35">
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
@@ -6075,11 +6075,11 @@
         <v>18.672413793103416</v>
       </c>
       <c r="AD22" s="7">
-        <f>1-_xlfn.F.DIST(AC22,Z22,Z24,TRUE)</f>
-        <v>8.3010310026554457E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="2:30" x14ac:dyDescent="0.3">
+        <f>1-_xlfn.F.DIST(AC22,Z22,Z23,TRUE)</f>
+        <v>9.9407927310468658E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:30" x14ac:dyDescent="0.35">
       <c r="X23" s="1"/>
       <c r="Y23" s="5" t="s">
         <v>36</v>
@@ -6098,7 +6098,7 @@
       <c r="AC23" s="7"/>
       <c r="AD23" s="7"/>
     </row>
-    <row r="24" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:30" x14ac:dyDescent="0.35">
       <c r="X24" s="1"/>
       <c r="Y24" s="5" t="s">
         <v>37</v>
@@ -6118,7 +6118,7 @@
       <c r="AC24" s="7"/>
       <c r="AD24" s="7"/>
     </row>
-    <row r="25" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:30" x14ac:dyDescent="0.35">
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
@@ -6127,7 +6127,7 @@
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
     </row>
-    <row r="26" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:30" x14ac:dyDescent="0.35">
       <c r="X26" s="1"/>
       <c r="Y26" s="5" t="s">
         <v>38</v>
@@ -6156,17 +6156,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C10366C-1A15-4AB6-85F6-3876593DB8A1}">
   <dimension ref="B2:E27"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="12"/>
-    <col min="2" max="2" width="13.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="12"/>
+    <col min="1" max="1" width="8.90625" style="12"/>
+    <col min="2" max="2" width="13.81640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.90625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.36328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.453125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.90625" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" s="13">
         <v>1</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="13">
         <v>2</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="13">
         <v>3</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="13">
         <v>4</v>
       </c>
@@ -6236,7 +6236,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="13">
         <v>5</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="13">
         <v>6</v>
       </c>
@@ -6264,7 +6264,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="13">
         <v>7</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="13">
         <v>8</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="13">
         <v>9</v>
       </c>
@@ -6306,7 +6306,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="13">
         <v>10</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="13">
         <v>11</v>
       </c>
@@ -6334,7 +6334,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="13">
         <v>12</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="13">
         <v>13</v>
       </c>
@@ -6362,7 +6362,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="13">
         <v>14</v>
       </c>
@@ -6376,7 +6376,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="13">
         <v>15</v>
       </c>
@@ -6390,7 +6390,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="13">
         <v>16</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="13">
         <v>17</v>
       </c>
@@ -6418,7 +6418,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="13">
         <v>18</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="13">
         <v>19</v>
       </c>
@@ -6446,7 +6446,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="13">
         <v>20</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="13">
         <v>21</v>
       </c>
@@ -6474,7 +6474,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="13">
         <v>22</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="13">
         <v>23</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="13">
         <v>24</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="13">
         <v>25</v>
       </c>
@@ -6538,16 +6538,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0765EF29-AA47-4480-9052-B1872DB3D306}">
   <dimension ref="B2:D32"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="12"/>
-    <col min="2" max="2" width="11.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" style="12"/>
+    <col min="2" max="2" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="12"/>
+    <col min="4" max="4" width="12.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.90625" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B2" s="14" t="s">
         <v>47</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B3" s="17" t="s">
         <v>50</v>
       </c>
@@ -6569,7 +6569,7 @@
         <v>15.29</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B4" s="17" t="s">
         <v>50</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>15.89</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B5" s="17" t="s">
         <v>50</v>
       </c>
@@ -6591,7 +6591,7 @@
         <v>16.02</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B6" s="17" t="s">
         <v>50</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>16.559999999999999</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" s="17" t="s">
         <v>50</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>15.46</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B8" s="17" t="s">
         <v>50</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>16.91</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" s="17" t="s">
         <v>50</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" s="17" t="s">
         <v>50</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>17.27</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" s="17" t="s">
         <v>50</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>16.850000000000001</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B12" s="17" t="s">
         <v>50</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B13" s="17" t="s">
         <v>50</v>
       </c>
@@ -6679,7 +6679,7 @@
         <v>17.23</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B14" s="17" t="s">
         <v>50</v>
       </c>
@@ -6690,7 +6690,7 @@
         <v>17.809999999999999</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B15" s="17" t="s">
         <v>50</v>
       </c>
@@ -6701,7 +6701,7 @@
         <v>17.739999999999998</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B16" s="17" t="s">
         <v>50</v>
       </c>
@@ -6712,7 +6712,7 @@
         <v>18.02</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="17" t="s">
         <v>50</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>18.37</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="17" t="s">
         <v>51</v>
       </c>
@@ -6734,7 +6734,7 @@
         <v>12.07</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="13" t="s">
         <v>51</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>12.42</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="13" t="s">
         <v>51</v>
       </c>
@@ -6756,7 +6756,7 @@
         <v>12.73</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="13" t="s">
         <v>51</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>13.02</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
         <v>51</v>
       </c>
@@ -6778,7 +6778,7 @@
         <v>12.05</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="13" t="s">
         <v>51</v>
       </c>
@@ -6789,7 +6789,7 @@
         <v>12.92</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
         <v>51</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>13.01</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="13" t="s">
         <v>51</v>
       </c>
@@ -6811,7 +6811,7 @@
         <v>12.21</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
         <v>51</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>13.49</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="13" t="s">
         <v>51</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>14.01</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="13" t="s">
         <v>51</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
         <v>51</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="13" t="s">
         <v>51</v>
       </c>
@@ -6866,7 +6866,7 @@
         <v>12.49</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="13" t="s">
         <v>51</v>
       </c>
@@ -6877,7 +6877,7 @@
         <v>13.55</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="13" t="s">
         <v>51</v>
       </c>
@@ -6896,15 +6896,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7D2400-CF1B-41F1-A0BB-204BF9B3BE29}">
   <dimension ref="B1:C19"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.90625" style="1"/>
+    <col min="2" max="2" width="5.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>52</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>41</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>41</v>
       </c>
@@ -6928,7 +6928,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
@@ -6936,7 +6936,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>41</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>41</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>42</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
@@ -6976,7 +6976,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
@@ -7000,7 +7000,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>54</v>
       </c>
@@ -7016,7 +7016,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>54</v>
       </c>
@@ -7024,7 +7024,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>54</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>54</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>54</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>54</v>
       </c>
